--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/115.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/115.xlsx
@@ -426,13 +426,13 @@
         <v>-22.2631644080406</v>
       </c>
       <c r="E2">
-        <v>-20.56346981046912</v>
+        <v>-18.23270007460932</v>
       </c>
       <c r="F2">
-        <v>-2.004499327522405</v>
+        <v>-0.5706318014421836</v>
       </c>
       <c r="G2">
-        <v>-18.86837276472486</v>
+        <v>-17.34891158046315</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-22.45264636854177</v>
       </c>
       <c r="E3">
-        <v>-22.26406448559004</v>
+        <v>-18.96265188421588</v>
       </c>
       <c r="F3">
-        <v>-1.756591329784388</v>
+        <v>-0.3677389451070979</v>
       </c>
       <c r="G3">
-        <v>-17.96517523045085</v>
+        <v>-17.10992663133723</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-22.4420136453588</v>
       </c>
       <c r="E4">
-        <v>-21.09464477285806</v>
+        <v>-21.00118505841545</v>
       </c>
       <c r="F4">
-        <v>-1.533594824950761</v>
+        <v>-0.5679048159521676</v>
       </c>
       <c r="G4">
-        <v>-17.45714391360464</v>
+        <v>-17.20805538291111</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-22.18528342794126</v>
       </c>
       <c r="E5">
-        <v>-23.4706678993132</v>
+        <v>-20.21455437385895</v>
       </c>
       <c r="F5">
-        <v>-1.673371055396941</v>
+        <v>-0.2951317138843184</v>
       </c>
       <c r="G5">
-        <v>-18.47298724475141</v>
+        <v>-16.88617798764505</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-21.69982513163906</v>
       </c>
       <c r="E6">
-        <v>-24.28106741228169</v>
+        <v>-20.02531745305446</v>
       </c>
       <c r="F6">
-        <v>-1.647169794446393</v>
+        <v>-0.2320912977964704</v>
       </c>
       <c r="G6">
-        <v>-18.1127266825068</v>
+        <v>-16.54771192124705</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-21.00775692560583</v>
       </c>
       <c r="E7">
-        <v>-23.47134487275915</v>
+        <v>-21.70089733636594</v>
       </c>
       <c r="F7">
-        <v>-0.8690495015658999</v>
+        <v>0.2350051998245036</v>
       </c>
       <c r="G7">
-        <v>-17.98142581015824</v>
+        <v>-16.49868866468742</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-20.12661026130588</v>
       </c>
       <c r="E8">
-        <v>-24.21010149037435</v>
+        <v>-22.3502893059048</v>
       </c>
       <c r="F8">
-        <v>-1.424000989192984</v>
+        <v>0.4831575659463459</v>
       </c>
       <c r="G8">
-        <v>-17.51764139264221</v>
+        <v>-16.51387667134622</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-19.0902319714787</v>
       </c>
       <c r="E9">
-        <v>-25.60327546323146</v>
+        <v>-23.20746228481352</v>
       </c>
       <c r="F9">
-        <v>-0.6130135628716147</v>
+        <v>0.3636779936035592</v>
       </c>
       <c r="G9">
-        <v>-17.87606921218386</v>
+        <v>-15.30716180314316</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-17.9365179615495</v>
       </c>
       <c r="E10">
-        <v>-26.08246883267885</v>
+        <v>-24.34898903028794</v>
       </c>
       <c r="F10">
-        <v>-0.9071477751554547</v>
+        <v>0.5526725016544748</v>
       </c>
       <c r="G10">
-        <v>-16.19542196223911</v>
+        <v>-15.21971491306382</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-16.71742648214238</v>
       </c>
       <c r="E11">
-        <v>-26.10769959147719</v>
+        <v>-25.34306431409698</v>
       </c>
       <c r="F11">
-        <v>-0.6768840030970678</v>
+        <v>0.8735472420680856</v>
       </c>
       <c r="G11">
-        <v>-16.23374638746436</v>
+        <v>-14.76140914307225</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-15.50400132488386</v>
       </c>
       <c r="E12">
-        <v>-26.26352808038475</v>
+        <v>-26.58341672304569</v>
       </c>
       <c r="F12">
-        <v>-0.4458804989479808</v>
+        <v>1.022686509268109</v>
       </c>
       <c r="G12">
-        <v>-15.71316261062408</v>
+        <v>-13.72778403051541</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-14.34407901712753</v>
       </c>
       <c r="E13">
-        <v>-27.40112588794589</v>
+        <v>-27.27743079505852</v>
       </c>
       <c r="F13">
-        <v>-0.6924771910873657</v>
+        <v>1.159943674442376</v>
       </c>
       <c r="G13">
-        <v>-14.60811927440503</v>
+        <v>-13.76528737656675</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-13.29276769565789</v>
       </c>
       <c r="E14">
-        <v>-29.86562695185951</v>
+        <v>-27.64022211070494</v>
       </c>
       <c r="F14">
-        <v>-0.8761900285780316</v>
+        <v>1.42130850063887</v>
       </c>
       <c r="G14">
-        <v>-14.9102829372636</v>
+        <v>-13.24351310019292</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-12.3717750783203</v>
       </c>
       <c r="E15">
-        <v>-30.71982000164266</v>
+        <v>-28.65258606058286</v>
       </c>
       <c r="F15">
-        <v>0.08472278560861729</v>
+        <v>1.48801858432112</v>
       </c>
       <c r="G15">
-        <v>-14.71545220603488</v>
+        <v>-13.03650585619125</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-11.59541682726862</v>
       </c>
       <c r="E16">
-        <v>-29.49998445663859</v>
+        <v>-29.39648227721254</v>
       </c>
       <c r="F16">
-        <v>-0.07659762424957244</v>
+        <v>1.796230900615537</v>
       </c>
       <c r="G16">
-        <v>-14.17018775520251</v>
+        <v>-11.6708227498353</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-10.96437059587843</v>
       </c>
       <c r="E17">
-        <v>-31.66098337317338</v>
+        <v>-30.16844589597541</v>
       </c>
       <c r="F17">
-        <v>0.01237980358733086</v>
+        <v>1.891344045804977</v>
       </c>
       <c r="G17">
-        <v>-14.35132904716772</v>
+        <v>-11.86743270350286</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-10.4583088593213</v>
       </c>
       <c r="E18">
-        <v>-31.63187351499765</v>
+        <v>-31.37081926396423</v>
       </c>
       <c r="F18">
-        <v>0.4673738534534041</v>
+        <v>2.071969557985409</v>
       </c>
       <c r="G18">
-        <v>-13.673143756968</v>
+        <v>-11.28444952019037</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-10.06152772092297</v>
       </c>
       <c r="E19">
-        <v>-33.50019770607744</v>
+        <v>-32.31539657520396</v>
       </c>
       <c r="F19">
-        <v>0.04588395156095966</v>
+        <v>2.273859261395704</v>
       </c>
       <c r="G19">
-        <v>-12.27619959487806</v>
+        <v>-10.75374258119805</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-9.736954819867377</v>
       </c>
       <c r="E20">
-        <v>-33.74400990029583</v>
+        <v>-32.22010529456709</v>
       </c>
       <c r="F20">
-        <v>0.4038944026420724</v>
+        <v>2.703990692034153</v>
       </c>
       <c r="G20">
-        <v>-12.7044308925523</v>
+        <v>-10.42874012465642</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-9.457615481564837</v>
       </c>
       <c r="E21">
-        <v>-33.09371668389948</v>
+        <v>-34.39169697658586</v>
       </c>
       <c r="F21">
-        <v>1.263242746306279</v>
+        <v>2.452521542831502</v>
       </c>
       <c r="G21">
-        <v>-13.12563014967038</v>
+        <v>-10.12386650891228</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-9.190491579690656</v>
       </c>
       <c r="E22">
-        <v>-33.74781631847504</v>
+        <v>-34.75775063972793</v>
       </c>
       <c r="F22">
-        <v>1.474062250318754</v>
+        <v>2.658713786531938</v>
       </c>
       <c r="G22">
-        <v>-12.53790715955273</v>
+        <v>-9.784269990106337</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-8.909545601220183</v>
       </c>
       <c r="E23">
-        <v>-34.17049278821416</v>
+        <v>-33.5644001233423</v>
       </c>
       <c r="F23">
-        <v>0.9997374187409512</v>
+        <v>2.857407648502233</v>
       </c>
       <c r="G23">
-        <v>-11.22375623530847</v>
+        <v>-9.697427487399839</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-8.605042349744332</v>
       </c>
       <c r="E24">
-        <v>-35.42977553438145</v>
+        <v>-34.13693276410389</v>
       </c>
       <c r="F24">
-        <v>1.085490012278756</v>
+        <v>2.485266906264166</v>
       </c>
       <c r="G24">
-        <v>-11.44316190537333</v>
+        <v>-9.616255521945241</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-8.274354263230546</v>
       </c>
       <c r="E25">
-        <v>-36.33578612525882</v>
+        <v>-34.4089099609216</v>
       </c>
       <c r="F25">
-        <v>1.512538259443985</v>
+        <v>2.669926567696232</v>
       </c>
       <c r="G25">
-        <v>-11.47369978485558</v>
+        <v>-9.457144998212136</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-7.941529970424625</v>
       </c>
       <c r="E26">
-        <v>-33.74953782456918</v>
+        <v>-35.53985017072905</v>
       </c>
       <c r="F26">
-        <v>0.9816674122162827</v>
+        <v>2.71843244933456</v>
       </c>
       <c r="G26">
-        <v>-12.30114917556303</v>
+        <v>-9.012587409237367</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-7.632107406950491</v>
       </c>
       <c r="E27">
-        <v>-35.7522661639374</v>
+        <v>-35.33993742021408</v>
       </c>
       <c r="F27">
-        <v>1.505258566708183</v>
+        <v>2.822667576363627</v>
       </c>
       <c r="G27">
-        <v>-11.96228888673178</v>
+        <v>-9.089730995787878</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-7.383161941640093</v>
       </c>
       <c r="E28">
-        <v>-35.61176094821279</v>
+        <v>-33.60561866913556</v>
       </c>
       <c r="F28">
-        <v>0.5703084436600763</v>
+        <v>2.460079567014644</v>
       </c>
       <c r="G28">
-        <v>-10.47728692032818</v>
+        <v>-8.819723874058054</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-7.224932842757687</v>
       </c>
       <c r="E29">
-        <v>-35.24834457426198</v>
+        <v>-34.68126717657555</v>
       </c>
       <c r="F29">
-        <v>0.4512977272672741</v>
+        <v>2.010055721565368</v>
       </c>
       <c r="G29">
-        <v>-10.59465424879397</v>
+        <v>-9.602741002569342</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-7.185037258419454</v>
       </c>
       <c r="E30">
-        <v>-33.92439425116144</v>
+        <v>-34.88382344609877</v>
       </c>
       <c r="F30">
-        <v>0.06348013193122676</v>
+        <v>2.306914434237016</v>
       </c>
       <c r="G30">
-        <v>-11.41539794201914</v>
+        <v>-9.353157735775799</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-7.279997889758663</v>
       </c>
       <c r="E31">
-        <v>-34.77349754046602</v>
+        <v>-34.63417806657465</v>
       </c>
       <c r="F31">
-        <v>0.49377557931543</v>
+        <v>2.439666937474859</v>
       </c>
       <c r="G31">
-        <v>-11.62955732082816</v>
+        <v>-9.528678094636346</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-7.510709667732486</v>
       </c>
       <c r="E32">
-        <v>-32.99266489915507</v>
+        <v>-33.10427830029852</v>
       </c>
       <c r="F32">
-        <v>0.8376540825047831</v>
+        <v>2.219422269153332</v>
       </c>
       <c r="G32">
-        <v>-11.21303651801736</v>
+        <v>-9.0922216461278</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-7.870141521900938</v>
       </c>
       <c r="E33">
-        <v>-33.32272267974486</v>
+        <v>-34.47549839809258</v>
       </c>
       <c r="F33">
-        <v>1.183070035593732</v>
+        <v>2.63761692551744</v>
       </c>
       <c r="G33">
-        <v>-10.72770693076317</v>
+        <v>-9.50188402289775</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-8.333060352897757</v>
       </c>
       <c r="E34">
-        <v>-33.90622602822098</v>
+        <v>-32.97641130663536</v>
       </c>
       <c r="F34">
-        <v>0.5802563078002956</v>
+        <v>2.714265761298478</v>
       </c>
       <c r="G34">
-        <v>-11.40550713613571</v>
+        <v>-9.120400717871981</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-8.875531470159439</v>
       </c>
       <c r="E35">
-        <v>-33.0293605978156</v>
+        <v>-32.78676114130405</v>
       </c>
       <c r="F35">
-        <v>1.331160589661811</v>
+        <v>2.754289160732139</v>
       </c>
       <c r="G35">
-        <v>-11.87032540850981</v>
+        <v>-9.334075803559353</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-9.463510504592367</v>
       </c>
       <c r="E36">
-        <v>-33.21068772765195</v>
+        <v>-31.52251530760359</v>
       </c>
       <c r="F36">
-        <v>1.533926705784268</v>
+        <v>2.76838300372337</v>
       </c>
       <c r="G36">
-        <v>-11.25874673969086</v>
+        <v>-10.10565264927238</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-10.06539539342299</v>
       </c>
       <c r="E37">
-        <v>-32.35096260038413</v>
+        <v>-31.81147913873986</v>
       </c>
       <c r="F37">
-        <v>1.539523155957582</v>
+        <v>2.872306664608985</v>
       </c>
       <c r="G37">
-        <v>-12.0326432319731</v>
+        <v>-10.39884448834359</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-10.65287316381385</v>
       </c>
       <c r="E38">
-        <v>-31.0966990101029</v>
+        <v>-31.30171398073041</v>
       </c>
       <c r="F38">
-        <v>1.018610941646335</v>
+        <v>2.723145859856489</v>
       </c>
       <c r="G38">
-        <v>-12.23236258244867</v>
+        <v>-10.72956578091204</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-11.19717294133251</v>
       </c>
       <c r="E39">
-        <v>-30.85177998506643</v>
+        <v>-29.57448891459469</v>
       </c>
       <c r="F39">
-        <v>0.7836031094721154</v>
+        <v>2.480742363510075</v>
       </c>
       <c r="G39">
-        <v>-12.70788490764634</v>
+        <v>-11.06017350609079</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-11.68112104605798</v>
       </c>
       <c r="E40">
-        <v>-30.10913803825686</v>
+        <v>-30.64974909677581</v>
       </c>
       <c r="F40">
-        <v>1.052792694155454</v>
+        <v>3.192366291498241</v>
       </c>
       <c r="G40">
-        <v>-12.03452688419559</v>
+        <v>-11.26292784715353</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-12.08452712542825</v>
       </c>
       <c r="E41">
-        <v>-31.08196756953373</v>
+        <v>-29.40845183225069</v>
       </c>
       <c r="F41">
-        <v>1.123775496901344</v>
+        <v>2.920209494778075</v>
       </c>
       <c r="G41">
-        <v>-12.67059172653459</v>
+        <v>-11.22629910054021</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-12.40417878902789</v>
       </c>
       <c r="E42">
-        <v>-29.16782307451278</v>
+        <v>-28.8898652533873</v>
       </c>
       <c r="F42">
-        <v>1.725050946427781</v>
+        <v>3.19106409794104</v>
       </c>
       <c r="G42">
-        <v>-12.20971828923765</v>
+        <v>-12.00135737416549</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-12.64060152822957</v>
       </c>
       <c r="E43">
-        <v>-29.36046770520929</v>
+        <v>-28.241989205982</v>
       </c>
       <c r="F43">
-        <v>1.532694095088903</v>
+        <v>3.007786153336844</v>
       </c>
       <c r="G43">
-        <v>-13.9068471697861</v>
+        <v>-12.28760071650745</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-12.80265144925957</v>
       </c>
       <c r="E44">
-        <v>-29.45683259097362</v>
+        <v>-28.57737348009588</v>
       </c>
       <c r="F44">
-        <v>1.337126491696773</v>
+        <v>3.375645892837243</v>
       </c>
       <c r="G44">
-        <v>-13.0621981937124</v>
+        <v>-12.09183272797052</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-12.90809172313142</v>
       </c>
       <c r="E45">
-        <v>-27.7271986622695</v>
+        <v>-28.14945981087615</v>
       </c>
       <c r="F45">
-        <v>1.120056127262774</v>
+        <v>2.887707671361833</v>
       </c>
       <c r="G45">
-        <v>-12.97220713302902</v>
+        <v>-12.40288858690642</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-12.97013186927513</v>
       </c>
       <c r="E46">
-        <v>-29.18257735774423</v>
+        <v>-26.69214364231838</v>
       </c>
       <c r="F46">
-        <v>1.715253016787469</v>
+        <v>3.537286880880316</v>
       </c>
       <c r="G46">
-        <v>-14.32278969266997</v>
+        <v>-12.86040330128689</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-13.01145690195262</v>
       </c>
       <c r="E47">
-        <v>-26.76586314333409</v>
+        <v>-26.78110958210753</v>
       </c>
       <c r="F47">
-        <v>1.017153015017408</v>
+        <v>3.707001137631073</v>
       </c>
       <c r="G47">
-        <v>-14.46175962725493</v>
+        <v>-12.57902769223506</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-13.04616048354702</v>
       </c>
       <c r="E48">
-        <v>-25.94498092498173</v>
+        <v>-25.37326231363981</v>
       </c>
       <c r="F48">
-        <v>1.41375710339495</v>
+        <v>3.672610636536449</v>
       </c>
       <c r="G48">
-        <v>-13.30710561694326</v>
+        <v>-13.28169393446565</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-13.08750461732817</v>
       </c>
       <c r="E49">
-        <v>-27.44891273744937</v>
+        <v>-24.64871383196684</v>
       </c>
       <c r="F49">
-        <v>1.081447579353094</v>
+        <v>3.688487126178504</v>
       </c>
       <c r="G49">
-        <v>-14.15452328765583</v>
+        <v>-13.32308598458546</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-13.14847860627378</v>
       </c>
       <c r="E50">
-        <v>-27.30121623631581</v>
+        <v>-25.50772253028113</v>
       </c>
       <c r="F50">
-        <v>1.213938318491653</v>
+        <v>3.691553742303668</v>
       </c>
       <c r="G50">
-        <v>-13.15253648342639</v>
+        <v>-13.60145271049603</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-13.23114993440041</v>
       </c>
       <c r="E51">
-        <v>-25.9794691918231</v>
+        <v>-23.98175377852395</v>
       </c>
       <c r="F51">
-        <v>1.162042757441069</v>
+        <v>3.531771610712477</v>
       </c>
       <c r="G51">
-        <v>-15.13872308898601</v>
+        <v>-13.33291804871559</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-13.34009619023478</v>
       </c>
       <c r="E52">
-        <v>-25.85881424962551</v>
+        <v>-24.2160322761462</v>
       </c>
       <c r="F52">
-        <v>1.304205514374715</v>
+        <v>3.846947183394827</v>
       </c>
       <c r="G52">
-        <v>-14.96070424755177</v>
+        <v>-13.72446316339551</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-13.46858762767134</v>
       </c>
       <c r="E53">
-        <v>-26.19504162563833</v>
+        <v>-23.10033435190089</v>
       </c>
       <c r="F53">
-        <v>1.397572461079053</v>
+        <v>3.34314075595139</v>
       </c>
       <c r="G53">
-        <v>-14.58455599909794</v>
+        <v>-13.66314721592862</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-13.61179289985893</v>
       </c>
       <c r="E54">
-        <v>-24.15969811773623</v>
+        <v>-22.92679241669293</v>
       </c>
       <c r="F54">
-        <v>0.7203075562242052</v>
+        <v>3.766797666969558</v>
       </c>
       <c r="G54">
-        <v>-14.39292995685482</v>
+        <v>-13.33516459443624</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-13.76415090988323</v>
       </c>
       <c r="E55">
-        <v>-22.63393287333397</v>
+        <v>-22.265547182033</v>
       </c>
       <c r="F55">
-        <v>1.534793178087597</v>
+        <v>3.667675223550569</v>
       </c>
       <c r="G55">
-        <v>-15.43992208171816</v>
+        <v>-14.21340863190839</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-13.91539126458152</v>
       </c>
       <c r="E56">
-        <v>-22.2056121894044</v>
+        <v>-20.81365926067679</v>
       </c>
       <c r="F56">
-        <v>1.421064960622447</v>
+        <v>3.399494590363841</v>
       </c>
       <c r="G56">
-        <v>-14.79007250793808</v>
+        <v>-13.64029536852261</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-14.06210609244263</v>
       </c>
       <c r="E57">
-        <v>-22.8874116669109</v>
+        <v>-20.79121945988874</v>
       </c>
       <c r="F57">
-        <v>1.048026268119746</v>
+        <v>3.496956985507619</v>
       </c>
       <c r="G57">
-        <v>-14.81508474649324</v>
+        <v>-13.79933148603487</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-14.19246692449674</v>
       </c>
       <c r="E58">
-        <v>-21.88603088438149</v>
+        <v>-20.65707488730811</v>
       </c>
       <c r="F58">
-        <v>0.5143248894766773</v>
+        <v>3.567263840452824</v>
       </c>
       <c r="G58">
-        <v>-14.43428676192264</v>
+        <v>-14.19776766106303</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-14.30345831923573</v>
       </c>
       <c r="E59">
-        <v>-22.24757208341914</v>
+        <v>-19.31979067924921</v>
       </c>
       <c r="F59">
-        <v>1.167099112067758</v>
+        <v>3.412171925096284</v>
       </c>
       <c r="G59">
-        <v>-14.36340243552933</v>
+        <v>-14.22657461688137</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-14.39037079049253</v>
       </c>
       <c r="E60">
-        <v>-21.64127798779802</v>
+        <v>-19.4594465632579</v>
       </c>
       <c r="F60">
-        <v>0.9399558000157164</v>
+        <v>3.181284392383589</v>
       </c>
       <c r="G60">
-        <v>-15.28927950806633</v>
+        <v>-14.52304816190361</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-14.44858964830864</v>
       </c>
       <c r="E61">
-        <v>-22.85973881985357</v>
+        <v>-19.62189527101724</v>
       </c>
       <c r="F61">
-        <v>1.638652226315793</v>
+        <v>3.078520445861894</v>
       </c>
       <c r="G61">
-        <v>-16.22082581248294</v>
+        <v>-14.62777295968693</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-14.4809539155279</v>
       </c>
       <c r="E62">
-        <v>-22.91282516700753</v>
+        <v>-18.33559588518194</v>
       </c>
       <c r="F62">
-        <v>1.341937649572233</v>
+        <v>3.027910511020455</v>
       </c>
       <c r="G62">
-        <v>-14.96543622212316</v>
+        <v>-14.47529764333215</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-14.48291560445071</v>
       </c>
       <c r="E63">
-        <v>-20.42694129458803</v>
+        <v>-18.73731940378731</v>
       </c>
       <c r="F63">
-        <v>0.7887191065518051</v>
+        <v>3.217484047885927</v>
       </c>
       <c r="G63">
-        <v>-14.81325853065176</v>
+        <v>-14.8725015469133</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-14.45661816031135</v>
       </c>
       <c r="E64">
-        <v>-22.29641384859913</v>
+        <v>-18.82118104685825</v>
       </c>
       <c r="F64">
-        <v>1.125337797823023</v>
+        <v>2.657486146040989</v>
       </c>
       <c r="G64">
-        <v>-16.08139769222224</v>
+        <v>-15.00404130239196</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-14.39958121139776</v>
       </c>
       <c r="E65">
-        <v>-20.69023412652554</v>
+        <v>-18.55084021530251</v>
       </c>
       <c r="F65">
-        <v>1.061906392321054</v>
+        <v>2.902484089092971</v>
       </c>
       <c r="G65">
-        <v>-15.75900859101632</v>
+        <v>-14.41003686078809</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-14.31103139125194</v>
       </c>
       <c r="E66">
-        <v>-20.55375544918034</v>
+        <v>-18.41031215691561</v>
       </c>
       <c r="F66">
-        <v>1.150430703188626</v>
+        <v>2.737508093886227</v>
       </c>
       <c r="G66">
-        <v>-15.17148532285989</v>
+        <v>-14.9643684275854</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-14.19647184027077</v>
       </c>
       <c r="E67">
-        <v>-20.1677601418621</v>
+        <v>-18.5329564873378</v>
       </c>
       <c r="F67">
-        <v>1.324391171246133</v>
+        <v>2.727390414428434</v>
       </c>
       <c r="G67">
-        <v>-15.85600036332077</v>
+        <v>-15.16978442275878</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-14.05584476422188</v>
       </c>
       <c r="E68">
-        <v>-21.41018915647324</v>
+        <v>-18.63522516300037</v>
       </c>
       <c r="F68">
-        <v>0.3997368266474217</v>
+        <v>2.62342864864229</v>
       </c>
       <c r="G68">
-        <v>-16.17029746166654</v>
+        <v>-14.58005899153975</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-13.89647712490295</v>
       </c>
       <c r="E69">
-        <v>-20.8503611891543</v>
+        <v>-19.25181091628442</v>
       </c>
       <c r="F69">
-        <v>0.3417030631420939</v>
+        <v>2.482684056702237</v>
       </c>
       <c r="G69">
-        <v>-15.17561291005844</v>
+        <v>-14.85301233854064</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-13.7189176086323</v>
       </c>
       <c r="E70">
-        <v>-20.70612431305433</v>
+        <v>-17.38877583982681</v>
       </c>
       <c r="F70">
-        <v>0.8336166197835383</v>
+        <v>2.479380527499873</v>
       </c>
       <c r="G70">
-        <v>-15.14816484679977</v>
+        <v>-14.32226232226256</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-13.528443529436</v>
       </c>
       <c r="E71">
-        <v>-20.5317683484267</v>
+        <v>-18.58459751695071</v>
       </c>
       <c r="F71">
-        <v>0.2084435990537374</v>
+        <v>2.182379335634944</v>
       </c>
       <c r="G71">
-        <v>-15.51081162960066</v>
+        <v>-14.27417371226655</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-13.33057198646293</v>
       </c>
       <c r="E72">
-        <v>-20.17423084510619</v>
+        <v>-17.27038024458992</v>
       </c>
       <c r="F72">
-        <v>0.5611442150829054</v>
+        <v>2.738616449471173</v>
       </c>
       <c r="G72">
-        <v>-14.54700696501626</v>
+        <v>-14.22241047925855</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-13.12393350580235</v>
       </c>
       <c r="E73">
-        <v>-19.18631477369187</v>
+        <v>-17.45893188552581</v>
       </c>
       <c r="F73">
-        <v>0.2252205240626358</v>
+        <v>2.668039546752655</v>
       </c>
       <c r="G73">
-        <v>-15.0441593091513</v>
+        <v>-14.41495028210856</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-12.91448772923925</v>
       </c>
       <c r="E74">
-        <v>-22.5193706921499</v>
+        <v>-18.18401613145967</v>
       </c>
       <c r="F74">
-        <v>-0.07304309972415976</v>
+        <v>2.082345688072876</v>
       </c>
       <c r="G74">
-        <v>-14.8794369899196</v>
+        <v>-13.42864491526565</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-12.69846324843213</v>
       </c>
       <c r="E75">
-        <v>-20.24240996221457</v>
+        <v>-18.17891183474146</v>
       </c>
       <c r="F75">
-        <v>-0.4428188530272339</v>
+        <v>2.340045816879385</v>
       </c>
       <c r="G75">
-        <v>-14.99291953043381</v>
+        <v>-14.33392321297877</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-12.47604603363581</v>
       </c>
       <c r="E76">
-        <v>-21.20027339648243</v>
+        <v>-18.06320336723174</v>
       </c>
       <c r="F76">
-        <v>0.1179370049912663</v>
+        <v>2.236546280104003</v>
       </c>
       <c r="G76">
-        <v>-14.93182549625717</v>
+        <v>-13.84458352203263</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-12.24695877270432</v>
       </c>
       <c r="E77">
-        <v>-21.46592940566376</v>
+        <v>-18.64077800654167</v>
       </c>
       <c r="F77">
-        <v>0.1486081364473208</v>
+        <v>1.997346908871618</v>
       </c>
       <c r="G77">
-        <v>-15.09185369671405</v>
+        <v>-13.5154130117513</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-12.00817890103069</v>
       </c>
       <c r="E78">
-        <v>-22.55885527221504</v>
+        <v>-18.344521136319</v>
       </c>
       <c r="F78">
-        <v>0.0004107229842808026</v>
+        <v>2.137773407728996</v>
       </c>
       <c r="G78">
-        <v>-14.5495185013129</v>
+        <v>-13.21765498039024</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-11.76625810245673</v>
       </c>
       <c r="E79">
-        <v>-23.3834172358012</v>
+        <v>-19.16771669337929</v>
       </c>
       <c r="F79">
-        <v>0.5944048230401111</v>
+        <v>1.820068000998496</v>
       </c>
       <c r="G79">
-        <v>-13.96761877700573</v>
+        <v>-12.52018020377907</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-11.52019909667828</v>
       </c>
       <c r="E80">
-        <v>-21.13637208703862</v>
+        <v>-19.00468653603447</v>
       </c>
       <c r="F80">
-        <v>0.7534207147837126</v>
+        <v>1.9445533975564</v>
       </c>
       <c r="G80">
-        <v>-14.75106667837456</v>
+        <v>-12.55076899278085</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-11.27712966840438</v>
       </c>
       <c r="E81">
-        <v>-22.72459332334365</v>
+        <v>-19.78380406130436</v>
       </c>
       <c r="F81">
-        <v>-0.0721269253766635</v>
+        <v>2.082499764409796</v>
       </c>
       <c r="G81">
-        <v>-13.27990557442074</v>
+        <v>-12.25125915179915</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-11.03910225404692</v>
       </c>
       <c r="E82">
-        <v>-23.95602878757796</v>
+        <v>-20.81629239665673</v>
       </c>
       <c r="F82">
-        <v>0.814443227878341</v>
+        <v>1.957891769476278</v>
       </c>
       <c r="G82">
-        <v>-13.206501879497</v>
+        <v>-11.72524763695394</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-10.81123252081426</v>
       </c>
       <c r="E83">
-        <v>-24.45389499514178</v>
+        <v>-22.48034711854181</v>
       </c>
       <c r="F83">
-        <v>0.1393751533757175</v>
+        <v>2.263145157407895</v>
       </c>
       <c r="G83">
-        <v>-13.87118570404378</v>
+        <v>-12.10897618232807</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-10.60002436767345</v>
       </c>
       <c r="E84">
-        <v>-24.60640506820081</v>
+        <v>-21.91166450467833</v>
       </c>
       <c r="F84">
-        <v>-0.003331012574164564</v>
+        <v>1.946256520936556</v>
       </c>
       <c r="G84">
-        <v>-14.79005684347054</v>
+        <v>-12.16139210148385</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-10.40511053240179</v>
       </c>
       <c r="E85">
-        <v>-26.80184241304108</v>
+        <v>-23.34893312217115</v>
       </c>
       <c r="F85">
-        <v>0.5156378518101145</v>
+        <v>2.25581410589312</v>
       </c>
       <c r="G85">
-        <v>-12.67262158045417</v>
+        <v>-12.04541760525741</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-10.23325000426248</v>
       </c>
       <c r="E86">
-        <v>-25.63355652700078</v>
+        <v>-23.29843422567256</v>
       </c>
       <c r="F86">
-        <v>0.3281153526339736</v>
+        <v>2.250621899012373</v>
       </c>
       <c r="G86">
-        <v>-12.69171265027669</v>
+        <v>-11.40538051502304</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-10.08368295186774</v>
       </c>
       <c r="E87">
-        <v>-28.60658093873774</v>
+        <v>-25.72903885535859</v>
       </c>
       <c r="F87">
-        <v>0.1926979914613244</v>
+        <v>2.129638839833505</v>
       </c>
       <c r="G87">
-        <v>-12.67044552483748</v>
+        <v>-11.02381497154265</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-9.961690737928539</v>
       </c>
       <c r="E88">
-        <v>-27.82614476887221</v>
+        <v>-26.01630402306301</v>
       </c>
       <c r="F88">
-        <v>0.2174264151696953</v>
+        <v>2.433755707688482</v>
       </c>
       <c r="G88">
-        <v>-13.07895003638127</v>
+        <v>-10.99331494785697</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-9.871270869329097</v>
       </c>
       <c r="E89">
-        <v>-29.91266207011319</v>
+        <v>-28.45742873703483</v>
       </c>
       <c r="F89">
-        <v>0.2865561600355224</v>
+        <v>2.005494730645554</v>
       </c>
       <c r="G89">
-        <v>-11.05889554661344</v>
+        <v>-10.68949607292764</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-9.816162090526134</v>
       </c>
       <c r="E90">
-        <v>-32.08917115434055</v>
+        <v>-29.49755067480224</v>
       </c>
       <c r="F90">
-        <v>0.5125091081297408</v>
+        <v>2.327179614379103</v>
       </c>
       <c r="G90">
-        <v>-12.61030571780889</v>
+        <v>-10.93052001357922</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-9.806170426000314</v>
       </c>
       <c r="E91">
-        <v>-32.95524446511837</v>
+        <v>-30.1992149620754</v>
       </c>
       <c r="F91">
-        <v>0.2380022330878322</v>
+        <v>2.087360624329424</v>
       </c>
       <c r="G91">
-        <v>-12.41185910532148</v>
+        <v>-10.60699523847616</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-9.843709954669231</v>
       </c>
       <c r="E92">
-        <v>-35.468900861667</v>
+        <v>-32.57590467894817</v>
       </c>
       <c r="F92">
-        <v>0.02594183470596436</v>
+        <v>2.207367866707794</v>
       </c>
       <c r="G92">
-        <v>-12.34032861964187</v>
+        <v>-10.53281484703656</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-9.935617570135683</v>
       </c>
       <c r="E93">
-        <v>-35.16312275448216</v>
+        <v>-34.64418522926182</v>
       </c>
       <c r="F93">
-        <v>0.0367801938041931</v>
+        <v>2.077792980827089</v>
       </c>
       <c r="G93">
-        <v>-12.00345380207216</v>
+        <v>-10.68881205784477</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-10.07714985178744</v>
       </c>
       <c r="E94">
-        <v>-36.23516835109786</v>
+        <v>-35.68901275546026</v>
       </c>
       <c r="F94">
-        <v>-0.04335689711003388</v>
+        <v>2.246991993053305</v>
       </c>
       <c r="G94">
-        <v>-13.13445838250523</v>
+        <v>-10.51521581774787</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-10.26475085888774</v>
       </c>
       <c r="E95">
-        <v>-38.89230573928534</v>
+        <v>-37.21809226249974</v>
       </c>
       <c r="F95">
-        <v>0.09399635868295775</v>
+        <v>1.747504673248065</v>
       </c>
       <c r="G95">
-        <v>-12.80338855553386</v>
+        <v>-10.64514082769692</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-10.48773278278853</v>
       </c>
       <c r="E96">
-        <v>-41.0043881328363</v>
+        <v>-39.3428045716895</v>
       </c>
       <c r="F96">
-        <v>0.3576375385023452</v>
+        <v>1.859099016283603</v>
       </c>
       <c r="G96">
-        <v>-12.53284753653515</v>
+        <v>-10.88686575327121</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-10.72592819806774</v>
       </c>
       <c r="E97">
-        <v>-42.78584998566296</v>
+        <v>-41.75615260832087</v>
       </c>
       <c r="F97">
-        <v>-0.3067205738494835</v>
+        <v>2.12044396166243</v>
       </c>
       <c r="G97">
-        <v>-13.74212485055439</v>
+        <v>-10.4263369342603</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-10.96580664577688</v>
       </c>
       <c r="E98">
-        <v>-43.60990941067881</v>
+        <v>-44.64118500832434</v>
       </c>
       <c r="F98">
-        <v>0.04974000182099136</v>
+        <v>1.758997442594505</v>
       </c>
       <c r="G98">
-        <v>-13.08591680832266</v>
+        <v>-11.05163245516096</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-11.18040117834</v>
       </c>
       <c r="E99">
-        <v>-47.00475680722764</v>
+        <v>-46.26893339511059</v>
       </c>
       <c r="F99">
-        <v>-0.5299440513514775</v>
+        <v>1.746401287867536</v>
       </c>
       <c r="G99">
-        <v>-13.14928480103816</v>
+        <v>-11.10678574002053</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-11.36236634647274</v>
       </c>
       <c r="E100">
-        <v>-47.51652173648999</v>
+        <v>-48.18878336418903</v>
       </c>
       <c r="F100">
-        <v>-0.1503132110572976</v>
+        <v>1.73244495386517</v>
       </c>
       <c r="G100">
-        <v>-12.48898963814904</v>
+        <v>-11.26490809692589</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-11.48724581021403</v>
       </c>
       <c r="E101">
-        <v>-49.34879293836177</v>
+        <v>-50.36949965148844</v>
       </c>
       <c r="F101">
-        <v>0.1465189938574604</v>
+        <v>1.223910205286553</v>
       </c>
       <c r="G101">
-        <v>-12.91976380105503</v>
+        <v>-11.43855785728691</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-11.56723328276887</v>
       </c>
       <c r="E102">
-        <v>-51.69872455297151</v>
+        <v>-51.84487605949222</v>
       </c>
       <c r="F102">
-        <v>-0.3825335869210971</v>
+        <v>1.456108215230477</v>
       </c>
       <c r="G102">
-        <v>-13.41047152216691</v>
+        <v>-11.39777541602913</v>
       </c>
     </row>
   </sheetData>
